--- a/Team-Data/2008-09/3-2-2008-09.xlsx
+++ b/Team-Data/2008-09/3-2-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" t="n">
         <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
@@ -679,16 +746,16 @@
         <v>35.9</v>
       </c>
       <c r="J2" t="n">
-        <v>78.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="K2" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L2" t="n">
         <v>7.4</v>
       </c>
       <c r="M2" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="N2" t="n">
         <v>0.365</v>
@@ -697,7 +764,7 @@
         <v>19.2</v>
       </c>
       <c r="P2" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="Q2" t="n">
         <v>0.736</v>
@@ -718,16 +785,16 @@
         <v>13.1</v>
       </c>
       <c r="W2" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y2" t="n">
         <v>4.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA2" t="n">
         <v>20.9</v>
@@ -736,13 +803,13 @@
         <v>98.40000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF2" t="n">
         <v>13</v>
@@ -754,13 +821,13 @@
         <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ2" t="n">
         <v>23</v>
       </c>
       <c r="AK2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL2" t="n">
         <v>9</v>
@@ -769,7 +836,7 @@
         <v>7</v>
       </c>
       <c r="AN2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO2" t="n">
         <v>16</v>
@@ -781,13 +848,13 @@
         <v>29</v>
       </c>
       <c r="AR2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS2" t="n">
         <v>21</v>
       </c>
       <c r="AT2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU2" t="n">
         <v>17</v>
@@ -796,7 +863,7 @@
         <v>6</v>
       </c>
       <c r="AW2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX2" t="n">
         <v>18</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -843,58 +910,58 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F3" t="n">
         <v>14</v>
       </c>
       <c r="G3" t="n">
-        <v>0.767</v>
+        <v>0.77</v>
       </c>
       <c r="H3" t="n">
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J3" t="n">
-        <v>77.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="K3" t="n">
-        <v>0.486</v>
+        <v>0.485</v>
       </c>
       <c r="L3" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
         <v>16.7</v>
       </c>
       <c r="N3" t="n">
-        <v>0.392</v>
+        <v>0.389</v>
       </c>
       <c r="O3" t="n">
         <v>20.2</v>
       </c>
       <c r="P3" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.774</v>
+        <v>0.771</v>
       </c>
       <c r="R3" t="n">
         <v>10.7</v>
       </c>
       <c r="S3" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T3" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="U3" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V3" t="n">
         <v>15.9</v>
@@ -903,10 +970,10 @@
         <v>8</v>
       </c>
       <c r="X3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z3" t="n">
         <v>23.3</v>
@@ -915,16 +982,16 @@
         <v>22.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.7</v>
+        <v>101.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
         <v>3</v>
@@ -933,7 +1000,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AI3" t="n">
         <v>9</v>
@@ -957,16 +1024,16 @@
         <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
         <v>19</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AT3" t="n">
         <v>8</v>
@@ -978,10 +1045,10 @@
         <v>26</v>
       </c>
       <c r="AW3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -1151,10 +1218,10 @@
         <v>27</v>
       </c>
       <c r="AT4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV4" t="n">
         <v>25</v>
@@ -1163,7 +1230,7 @@
         <v>16</v>
       </c>
       <c r="AX4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY4" t="n">
         <v>29</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5" t="n">
         <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>0.441</v>
+        <v>0.45</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
@@ -1225,10 +1292,10 @@
         <v>37.7</v>
       </c>
       <c r="J5" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L5" t="n">
         <v>5.9</v>
@@ -1237,34 +1304,34 @@
         <v>15.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.375</v>
+        <v>0.376</v>
       </c>
       <c r="O5" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="P5" t="n">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.788</v>
+        <v>0.787</v>
       </c>
       <c r="R5" t="n">
         <v>12.1</v>
       </c>
       <c r="S5" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T5" t="n">
         <v>42.4</v>
       </c>
       <c r="U5" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V5" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W5" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X5" t="n">
         <v>5.6</v>
@@ -1276,37 +1343,37 @@
         <v>21.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>100.7</v>
+        <v>100.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.7</v>
+        <v>-1.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
       </c>
       <c r="AF5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG5" t="n">
         <v>18</v>
       </c>
       <c r="AH5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI5" t="n">
         <v>8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL5" t="n">
         <v>24</v>
@@ -1315,13 +1382,13 @@
         <v>24</v>
       </c>
       <c r="AN5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
@@ -1342,7 +1409,7 @@
         <v>19</v>
       </c>
       <c r="AW5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX5" t="n">
         <v>5</v>
@@ -1354,7 +1421,7 @@
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BB5" t="n">
         <v>11</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -1392,61 +1459,61 @@
         <v>58</v>
       </c>
       <c r="E6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.793</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J6" t="n">
-        <v>78.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.471</v>
+        <v>0.47</v>
       </c>
       <c r="L6" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="M6" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0.389</v>
+        <v>0.383</v>
       </c>
       <c r="O6" t="n">
         <v>18.6</v>
       </c>
       <c r="P6" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.757</v>
+        <v>0.754</v>
       </c>
       <c r="R6" t="n">
         <v>10.8</v>
       </c>
       <c r="S6" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T6" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U6" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V6" t="n">
         <v>13.1</v>
       </c>
       <c r="W6" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X6" t="n">
         <v>5.6</v>
@@ -1458,31 +1525,31 @@
         <v>20.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.4</v>
+        <v>100</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF6" t="n">
         <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
         <v>26</v>
       </c>
       <c r="AI6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ6" t="n">
         <v>25</v>
@@ -1491,19 +1558,19 @@
         <v>5</v>
       </c>
       <c r="AL6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN6" t="n">
         <v>4</v>
       </c>
       <c r="AO6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
         <v>22</v>
@@ -1515,7 +1582,7 @@
         <v>10</v>
       </c>
       <c r="AT6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU6" t="n">
         <v>24</v>
@@ -1524,19 +1591,19 @@
         <v>7</v>
       </c>
       <c r="AW6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX6" t="n">
         <v>4</v>
       </c>
       <c r="AY6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ6" t="n">
         <v>6</v>
       </c>
       <c r="BA6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB6" t="n">
         <v>12</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -1571,22 +1638,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" t="n">
         <v>36</v>
       </c>
       <c r="F7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
       </c>
       <c r="I7" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="J7" t="n">
         <v>83.09999999999999</v>
@@ -1598,16 +1665,16 @@
         <v>6.7</v>
       </c>
       <c r="M7" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0.345</v>
+        <v>0.346</v>
       </c>
       <c r="O7" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P7" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="Q7" t="n">
         <v>0.8169999999999999</v>
@@ -1616,52 +1683,52 @@
         <v>11.3</v>
       </c>
       <c r="S7" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T7" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U7" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V7" t="n">
         <v>13.5</v>
       </c>
       <c r="W7" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y7" t="n">
         <v>4.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA7" t="n">
         <v>19.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>100.9</v>
+        <v>101.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG7" t="n">
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI7" t="n">
         <v>7</v>
@@ -1679,7 +1746,7 @@
         <v>11</v>
       </c>
       <c r="AN7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO7" t="n">
         <v>24</v>
@@ -1694,25 +1761,25 @@
         <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AV7" t="n">
         <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX7" t="n">
         <v>7</v>
       </c>
       <c r="AY7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ7" t="n">
         <v>3</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1901,7 @@
         <v>6</v>
       </c>
       <c r="AE8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF8" t="n">
         <v>6</v>
@@ -1846,7 +1913,7 @@
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ8" t="n">
         <v>24</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-0.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE9" t="n">
         <v>15</v>
@@ -2028,7 +2095,7 @@
         <v>14</v>
       </c>
       <c r="AI9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ9" t="n">
         <v>22</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2207,7 +2274,7 @@
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI10" t="n">
         <v>3</v>
@@ -2258,7 +2325,7 @@
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ10" t="n">
         <v>24</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -2383,10 +2450,10 @@
         <v>7</v>
       </c>
       <c r="AF11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH11" t="n">
         <v>21</v>
@@ -2404,13 +2471,13 @@
         <v>6</v>
       </c>
       <c r="AM11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN11" t="n">
         <v>7</v>
       </c>
       <c r="AO11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
@@ -2431,10 +2498,10 @@
         <v>19</v>
       </c>
       <c r="AV11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX11" t="n">
         <v>28</v>
@@ -2446,7 +2513,7 @@
         <v>2</v>
       </c>
       <c r="BA11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB11" t="n">
         <v>17</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2629,7 @@
         <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF12" t="n">
         <v>22</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -2663,40 +2730,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E13" t="n">
         <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G13" t="n">
-        <v>0.246</v>
+        <v>0.25</v>
       </c>
       <c r="H13" t="n">
         <v>48.6</v>
       </c>
       <c r="I13" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="J13" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="K13" t="n">
-        <v>0.435</v>
+        <v>0.436</v>
       </c>
       <c r="L13" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M13" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="N13" t="n">
         <v>0.348</v>
       </c>
       <c r="O13" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P13" t="n">
         <v>22.6</v>
@@ -2705,22 +2772,22 @@
         <v>0.745</v>
       </c>
       <c r="R13" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S13" t="n">
         <v>29</v>
       </c>
       <c r="T13" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="U13" t="n">
         <v>21</v>
       </c>
       <c r="V13" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W13" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X13" t="n">
         <v>6.1</v>
@@ -2729,34 +2796,34 @@
         <v>5.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.8</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>-8.6</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE13" t="n">
         <v>26</v>
       </c>
       <c r="AF13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI13" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AJ13" t="n">
         <v>8</v>
@@ -2765,13 +2832,13 @@
         <v>30</v>
       </c>
       <c r="AL13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO13" t="n">
         <v>28</v>
@@ -2792,7 +2859,7 @@
         <v>22</v>
       </c>
       <c r="AU13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV13" t="n">
         <v>18</v>
@@ -2807,7 +2874,7 @@
         <v>22</v>
       </c>
       <c r="AZ13" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BA13" t="n">
         <v>26</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F14" t="n">
         <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>0.797</v>
+        <v>0.8</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
@@ -2863,40 +2930,40 @@
         <v>40.7</v>
       </c>
       <c r="J14" t="n">
-        <v>85.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.477</v>
+        <v>0.476</v>
       </c>
       <c r="L14" t="n">
         <v>6.9</v>
       </c>
       <c r="M14" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.363</v>
+        <v>0.366</v>
       </c>
       <c r="O14" t="n">
         <v>20.6</v>
       </c>
       <c r="P14" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
       <c r="R14" t="n">
         <v>12.7</v>
       </c>
       <c r="S14" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T14" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="U14" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="V14" t="n">
         <v>13.7</v>
@@ -2908,31 +2975,31 @@
         <v>5.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>109.1</v>
+        <v>108.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
         <v>16</v>
@@ -2953,7 +3020,7 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO14" t="n">
         <v>5</v>
@@ -2962,13 +3029,13 @@
         <v>6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AR14" t="n">
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2989,7 +3056,7 @@
         <v>13</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA14" t="n">
         <v>6</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3147,7 +3214,7 @@
         <v>24</v>
       </c>
       <c r="AR15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS15" t="n">
         <v>26</v>
@@ -3162,7 +3229,7 @@
         <v>24</v>
       </c>
       <c r="AW15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX15" t="n">
         <v>22</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E16" t="n">
         <v>31</v>
       </c>
       <c r="F16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G16" t="n">
-        <v>0.525</v>
+        <v>0.534</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
@@ -3227,7 +3294,7 @@
         <v>36.6</v>
       </c>
       <c r="J16" t="n">
-        <v>81</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K16" t="n">
         <v>0.452</v>
@@ -3236,10 +3303,10 @@
         <v>6.8</v>
       </c>
       <c r="M16" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0.348</v>
+        <v>0.349</v>
       </c>
       <c r="O16" t="n">
         <v>16.8</v>
@@ -3251,22 +3318,22 @@
         <v>0.752</v>
       </c>
       <c r="R16" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="S16" t="n">
         <v>29.1</v>
       </c>
       <c r="T16" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="U16" t="n">
         <v>19.8</v>
       </c>
       <c r="V16" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="W16" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X16" t="n">
         <v>5.5</v>
@@ -3278,16 +3345,16 @@
         <v>20.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AB16" t="n">
         <v>96.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
@@ -3308,7 +3375,7 @@
         <v>12</v>
       </c>
       <c r="AK16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL16" t="n">
         <v>12</v>
@@ -3317,7 +3384,7 @@
         <v>10</v>
       </c>
       <c r="AN16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO16" t="n">
         <v>29</v>
@@ -3344,7 +3411,7 @@
         <v>3</v>
       </c>
       <c r="AW16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX16" t="n">
         <v>6</v>
@@ -3353,10 +3420,10 @@
         <v>5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB16" t="n">
         <v>23</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E17" t="n">
         <v>29</v>
       </c>
       <c r="F17" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G17" t="n">
-        <v>0.475</v>
+        <v>0.468</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3412,7 +3479,7 @@
         <v>81.5</v>
       </c>
       <c r="K17" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L17" t="n">
         <v>6.1</v>
@@ -3421,31 +3488,31 @@
         <v>16.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="O17" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="P17" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.78</v>
+        <v>0.779</v>
       </c>
       <c r="R17" t="n">
         <v>12</v>
       </c>
       <c r="S17" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="T17" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U17" t="n">
         <v>21.6</v>
       </c>
       <c r="V17" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W17" t="n">
         <v>7.2</v>
@@ -3457,19 +3524,19 @@
         <v>4.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="AA17" t="n">
         <v>23.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.8</v>
+        <v>99.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>15</v>
@@ -3499,16 +3566,16 @@
         <v>21</v>
       </c>
       <c r="AN17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AP17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR17" t="n">
         <v>7</v>
@@ -3517,13 +3584,13 @@
         <v>25</v>
       </c>
       <c r="AT17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU17" t="n">
         <v>11</v>
       </c>
       <c r="AV17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW17" t="n">
         <v>15</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-4.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3666,10 +3733,10 @@
         <v>10</v>
       </c>
       <c r="AI18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK18" t="n">
         <v>28</v>
@@ -3681,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="AN18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO18" t="n">
         <v>18</v>
       </c>
       <c r="AP18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ18" t="n">
         <v>17</v>
@@ -3699,10 +3766,10 @@
         <v>19</v>
       </c>
       <c r="AT18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV18" t="n">
         <v>16</v>
@@ -3720,10 +3787,10 @@
         <v>20</v>
       </c>
       <c r="BA18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -3833,16 +3900,16 @@
         <v>-2.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH19" t="n">
         <v>7</v>
@@ -3860,16 +3927,16 @@
         <v>7</v>
       </c>
       <c r="AM19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO19" t="n">
         <v>15</v>
       </c>
       <c r="AP19" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AQ19" t="n">
         <v>10</v>
@@ -3890,7 +3957,7 @@
         <v>9</v>
       </c>
       <c r="AW19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX19" t="n">
         <v>19</v>
@@ -3902,7 +3969,7 @@
         <v>26</v>
       </c>
       <c r="BA19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB19" t="n">
         <v>20</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F20" t="n">
         <v>22</v>
       </c>
       <c r="G20" t="n">
-        <v>0.627</v>
+        <v>0.621</v>
       </c>
       <c r="H20" t="n">
         <v>48.1</v>
@@ -3955,7 +4022,7 @@
         <v>35</v>
       </c>
       <c r="J20" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K20" t="n">
         <v>0.455</v>
@@ -3964,28 +4031,28 @@
         <v>7.5</v>
       </c>
       <c r="M20" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="N20" t="n">
-        <v>0.379</v>
+        <v>0.376</v>
       </c>
       <c r="O20" t="n">
         <v>18.7</v>
       </c>
       <c r="P20" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="R20" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="S20" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="T20" t="n">
-        <v>39.6</v>
+        <v>39.4</v>
       </c>
       <c r="U20" t="n">
         <v>19.8</v>
@@ -4003,7 +4070,7 @@
         <v>3.7</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA20" t="n">
         <v>21</v>
@@ -4012,16 +4079,16 @@
         <v>96.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AE20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG20" t="n">
         <v>9</v>
@@ -4045,7 +4112,7 @@
         <v>9</v>
       </c>
       <c r="AN20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AO20" t="n">
         <v>20</v>
@@ -4063,28 +4130,28 @@
         <v>16</v>
       </c>
       <c r="AT20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV20" t="n">
         <v>4</v>
       </c>
       <c r="AW20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY20" t="n">
         <v>1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BA20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB20" t="n">
         <v>25</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE21" t="n">
         <v>22</v>
@@ -4209,7 +4276,7 @@
         <v>22</v>
       </c>
       <c r="AH21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI21" t="n">
         <v>5</v>
@@ -4248,7 +4315,7 @@
         <v>7</v>
       </c>
       <c r="AU21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV21" t="n">
         <v>17</v>
@@ -4263,7 +4330,7 @@
         <v>23</v>
       </c>
       <c r="AZ21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -4301,31 +4368,31 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F22" t="n">
         <v>45</v>
       </c>
       <c r="G22" t="n">
-        <v>0.25</v>
+        <v>0.237</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J22" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K22" t="n">
         <v>0.449</v>
       </c>
       <c r="L22" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="M22" t="n">
         <v>11.5</v>
@@ -4334,13 +4401,13 @@
         <v>0.368</v>
       </c>
       <c r="O22" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="P22" t="n">
-        <v>26.1</v>
+        <v>26.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.78</v>
+        <v>0.779</v>
       </c>
       <c r="R22" t="n">
         <v>12.4</v>
@@ -4349,16 +4416,16 @@
         <v>30.8</v>
       </c>
       <c r="T22" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U22" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V22" t="n">
         <v>16.5</v>
       </c>
       <c r="W22" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X22" t="n">
         <v>4.4</v>
@@ -4367,34 +4434,34 @@
         <v>5.1</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>98.3</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC22" t="n">
-        <v>-5.8</v>
+        <v>-6</v>
       </c>
       <c r="AD22" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AF22" t="n">
         <v>27</v>
       </c>
       <c r="AG22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ22" t="n">
         <v>9</v>
@@ -4409,16 +4476,16 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP22" t="n">
         <v>8</v>
       </c>
-      <c r="AP22" t="n">
-        <v>9</v>
-      </c>
       <c r="AQ22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR22" t="n">
         <v>4</v>
@@ -4427,7 +4494,7 @@
         <v>11</v>
       </c>
       <c r="AT22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU22" t="n">
         <v>20</v>
@@ -4442,13 +4509,13 @@
         <v>21</v>
       </c>
       <c r="AY22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ22" t="n">
         <v>16</v>
       </c>
       <c r="BA22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB22" t="n">
         <v>19</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>6.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E24" t="n">
         <v>29</v>
       </c>
       <c r="F24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G24" t="n">
-        <v>0.492</v>
+        <v>0.5</v>
       </c>
       <c r="H24" t="n">
         <v>48.1</v>
@@ -4692,19 +4759,19 @@
         <v>4.2</v>
       </c>
       <c r="M24" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.318</v>
+        <v>0.319</v>
       </c>
       <c r="O24" t="n">
         <v>19.5</v>
       </c>
       <c r="P24" t="n">
-        <v>26.1</v>
+        <v>26.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="R24" t="n">
         <v>12.8</v>
@@ -4719,13 +4786,13 @@
         <v>20.4</v>
       </c>
       <c r="V24" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W24" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y24" t="n">
         <v>4.8</v>
@@ -4734,28 +4801,28 @@
         <v>20.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>96.59999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
       </c>
       <c r="AF24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI24" t="n">
         <v>18</v>
@@ -4779,7 +4846,7 @@
         <v>11</v>
       </c>
       <c r="AP24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ24" t="n">
         <v>27</v>
@@ -4797,7 +4864,7 @@
         <v>21</v>
       </c>
       <c r="AV24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW24" t="n">
         <v>5</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE25" t="n">
         <v>12</v>
@@ -4949,7 +5016,7 @@
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM25" t="n">
         <v>19</v>
@@ -4991,7 +5058,7 @@
         <v>8</v>
       </c>
       <c r="AZ25" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA25" t="n">
         <v>5</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
         <v>37</v>
       </c>
       <c r="F26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G26" t="n">
-        <v>0.638</v>
+        <v>0.627</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J26" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0.465</v>
+        <v>0.462</v>
       </c>
       <c r="L26" t="n">
         <v>7.3</v>
       </c>
       <c r="M26" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.38</v>
+        <v>0.381</v>
       </c>
       <c r="O26" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="P26" t="n">
-        <v>24.4</v>
+        <v>24.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.762</v>
+        <v>0.76</v>
       </c>
       <c r="R26" t="n">
         <v>12.9</v>
@@ -5077,7 +5144,7 @@
         <v>28.3</v>
       </c>
       <c r="T26" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U26" t="n">
         <v>20.6</v>
@@ -5089,46 +5156,46 @@
         <v>6.9</v>
       </c>
       <c r="X26" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y26" t="n">
         <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.40000000000001</v>
+        <v>99</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
       </c>
       <c r="AF26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ26" t="n">
         <v>21</v>
       </c>
       <c r="AK26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL26" t="n">
         <v>10</v>
@@ -5140,7 +5207,7 @@
         <v>6</v>
       </c>
       <c r="AO26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP26" t="n">
         <v>18</v>
@@ -5164,7 +5231,7 @@
         <v>5</v>
       </c>
       <c r="AW26" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AX26" t="n">
         <v>17</v>
@@ -5176,10 +5243,10 @@
         <v>17</v>
       </c>
       <c r="BA26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
         <v>5</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-9.199999999999999</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
@@ -5301,7 +5368,7 @@
         <v>30</v>
       </c>
       <c r="AH27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI27" t="n">
         <v>21</v>
@@ -5316,7 +5383,7 @@
         <v>15</v>
       </c>
       <c r="AM27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN27" t="n">
         <v>21</v>
@@ -5340,19 +5407,19 @@
         <v>30</v>
       </c>
       <c r="AU27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX27" t="n">
         <v>26</v>
       </c>
       <c r="AY27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ27" t="n">
         <v>28</v>
@@ -5361,7 +5428,7 @@
         <v>11</v>
       </c>
       <c r="BB27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -5393,25 +5460,25 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E28" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F28" t="n">
         <v>19</v>
       </c>
       <c r="G28" t="n">
-        <v>0.678</v>
+        <v>0.672</v>
       </c>
       <c r="H28" t="n">
         <v>48.7</v>
       </c>
       <c r="I28" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J28" t="n">
-        <v>79.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K28" t="n">
         <v>0.464</v>
@@ -5420,58 +5487,58 @@
         <v>7.9</v>
       </c>
       <c r="M28" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.394</v>
+        <v>0.395</v>
       </c>
       <c r="O28" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="P28" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.772</v>
+        <v>0.77</v>
       </c>
       <c r="R28" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>32.2</v>
+        <v>32</v>
       </c>
       <c r="T28" t="n">
-        <v>41</v>
+        <v>40.8</v>
       </c>
       <c r="U28" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V28" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="W28" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="X28" t="n">
         <v>4.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z28" t="n">
         <v>18.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.3</v>
+        <v>97.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5486,16 +5553,16 @@
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ28" t="n">
         <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM28" t="n">
         <v>8</v>
@@ -5510,7 +5577,7 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
@@ -5519,7 +5586,7 @@
         <v>4</v>
       </c>
       <c r="AT28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU28" t="n">
         <v>7</v>
@@ -5531,7 +5598,7 @@
         <v>30</v>
       </c>
       <c r="AX28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY28" t="n">
         <v>9</v>
@@ -5546,7 +5613,7 @@
         <v>22</v>
       </c>
       <c r="BC28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
         <v>23</v>
@@ -5674,7 +5741,7 @@
         <v>20</v>
       </c>
       <c r="AK29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL29" t="n">
         <v>22</v>
@@ -5689,7 +5756,7 @@
         <v>19</v>
       </c>
       <c r="AP29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5704,7 +5771,7 @@
         <v>27</v>
       </c>
       <c r="AU29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV29" t="n">
         <v>8</v>
@@ -5722,7 +5789,7 @@
         <v>4</v>
       </c>
       <c r="BA29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB29" t="n">
         <v>21</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5914,7 @@
         <v>10</v>
       </c>
       <c r="AH30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI30" t="n">
         <v>6</v>
@@ -5883,7 +5950,7 @@
         <v>22</v>
       </c>
       <c r="AT30" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
@@ -5895,7 +5962,7 @@
         <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY30" t="n">
         <v>16</v>
@@ -5910,7 +5977,7 @@
         <v>6</v>
       </c>
       <c r="BC30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
@@ -5939,22 +6006,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E31" t="n">
         <v>14</v>
       </c>
       <c r="F31" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G31" t="n">
-        <v>0.233</v>
+        <v>0.237</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
       </c>
       <c r="I31" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J31" t="n">
         <v>81.3</v>
@@ -5963,22 +6030,22 @@
         <v>0.446</v>
       </c>
       <c r="L31" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="M31" t="n">
-        <v>15.3</v>
+        <v>15.5</v>
       </c>
       <c r="N31" t="n">
         <v>0.322</v>
       </c>
       <c r="O31" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="P31" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="R31" t="n">
         <v>11.9</v>
@@ -6005,28 +6072,28 @@
         <v>5.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AB31" t="n">
         <v>94.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.5</v>
+        <v>-7.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF31" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG31" t="n">
         <v>28</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>29</v>
       </c>
       <c r="AH31" t="n">
         <v>29</v>
@@ -6053,7 +6120,7 @@
         <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ31" t="n">
         <v>18</v>
@@ -6065,7 +6132,7 @@
         <v>30</v>
       </c>
       <c r="AT31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU31" t="n">
         <v>22</v>
@@ -6086,7 +6153,7 @@
         <v>13</v>
       </c>
       <c r="BA31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB31" t="n">
         <v>27</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-2-2008-09</t>
+          <t>2009-03-02</t>
         </is>
       </c>
     </row>
